--- a/result.xlsx
+++ b/result.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D18"/>
+  <dimension ref="A1:D6"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -462,153 +462,21 @@
     </row>
     <row r="6">
       <c r="A6" t="str">
-        <v>long5</v>
+        <v>tuan</v>
       </c>
       <c r="B6" t="str">
-        <v>ORDER</v>
+        <v>LOGIN</v>
       </c>
       <c r="C6" t="str">
-        <v>SUCCESS</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="str">
-        <v>long4</v>
-      </c>
-      <c r="B7" t="str">
-        <v>ORDER</v>
-      </c>
-      <c r="C7" t="str">
-        <v>SUCCESS</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="str">
-        <v>long</v>
-      </c>
-      <c r="B8" t="str">
-        <v>ORDER</v>
-      </c>
-      <c r="C8" t="str">
-        <v>SKIP_NO_LOGIN</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="str">
-        <v>long3</v>
-      </c>
-      <c r="B9" t="str">
-        <v>ORDER</v>
-      </c>
-      <c r="C9" t="str">
-        <v>SUCCESS</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="str">
-        <v>long5</v>
-      </c>
-      <c r="B10" t="str">
-        <v>LOGIN</v>
-      </c>
-      <c r="C10" t="str">
-        <v>SUCCESS</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="str">
-        <v>long4</v>
-      </c>
-      <c r="B11" t="str">
-        <v>LOGIN</v>
-      </c>
-      <c r="C11" t="str">
-        <v>SUCCESS</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="str">
-        <v>long</v>
-      </c>
-      <c r="B12" t="str">
-        <v>LOGIN</v>
-      </c>
-      <c r="C12" t="str">
-        <v>FAIL</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="str">
-        <v>long</v>
-      </c>
-      <c r="B13" t="str">
-        <v>LOGIN</v>
-      </c>
-      <c r="C13" t="str">
         <v>ERROR</v>
       </c>
-      <c r="D13" t="str">
-        <v>Error: Login failed: long</v>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="str">
-        <v>long3</v>
-      </c>
-      <c r="B14" t="str">
-        <v>LOGIN</v>
-      </c>
-      <c r="C14" t="str">
-        <v>SUCCESS</v>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="str">
-        <v>long5</v>
-      </c>
-      <c r="B15" t="str">
-        <v>ORDER</v>
-      </c>
-      <c r="C15" t="str">
-        <v>SUCCESS</v>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="str">
-        <v>long4</v>
-      </c>
-      <c r="B16" t="str">
-        <v>ORDER</v>
-      </c>
-      <c r="C16" t="str">
-        <v>SUCCESS</v>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="str">
-        <v>long</v>
-      </c>
-      <c r="B17" t="str">
-        <v>ORDER</v>
-      </c>
-      <c r="C17" t="str">
-        <v>SKIP_NO_LOGIN</v>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="str">
-        <v>long3</v>
-      </c>
-      <c r="B18" t="str">
-        <v>ORDER</v>
-      </c>
-      <c r="C18" t="str">
-        <v>SUCCESS</v>
+      <c r="D6" t="str">
+        <v>Error: Login failed: tuan</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:D18"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:D6"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/result.xlsx
+++ b/result.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D6"/>
+  <dimension ref="A1:D9"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -474,9 +474,62 @@
         <v>Error: Login failed: tuan</v>
       </c>
     </row>
+    <row r="7">
+      <c r="A7" t="str">
+        <v>long</v>
+      </c>
+      <c r="B7" t="str">
+        <v>ORDER</v>
+      </c>
+      <c r="C7" t="str">
+        <v>SKIP_NO_LOGIN</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="str">
+        <v>tuan</v>
+      </c>
+      <c r="B8" t="str">
+        <v>ORDER</v>
+      </c>
+      <c r="C8" t="str">
+        <v>SKIP_NO_LOGIN</v>
+      </c>
+    </row>
+    <row r="9" xml:space="preserve">
+      <c r="A9" t="str">
+        <v>long5</v>
+      </c>
+      <c r="B9" t="str">
+        <v>ORDER</v>
+      </c>
+      <c r="C9" t="str">
+        <v>ERROR</v>
+      </c>
+      <c r="D9" t="str" xml:space="preserve">
+        <v xml:space="preserve">Error: locator.click: Target page, context or browser has been closed
+Call log:
+_x001b_[2m  - waiting for getByText('Thêm vào giỏ hàng', { exact: true })_x001b_[22m
+_x001b_[2m    - locator resolved to &lt;span class="inline-flex items-center gap-2"&gt;Thêm vào giỏ hàng&lt;/span&gt;_x001b_[22m
+_x001b_[2m  - attempting click action_x001b_[22m
+_x001b_[2m    2 × waiting for element to be visible, enabled and stable_x001b_[22m
+_x001b_[2m      - element is not enabled_x001b_[22m
+_x001b_[2m    - retrying click action_x001b_[22m
+_x001b_[2m    - waiting 20ms_x001b_[22m
+_x001b_[2m    2 × waiting for element to be visible, enabled and stable_x001b_[22m
+_x001b_[2m      - element is not enabled_x001b_[22m
+_x001b_[2m    - retrying click action_x001b_[22m
+_x001b_[2m      - waiting 100ms_x001b_[22m
+_x001b_[2m    8 × waiting for element to be visible, enabled and stable_x001b_[22m
+_x001b_[2m      - element is not enabled_x001b_[22m
+_x001b_[2m    - retrying click action_x001b_[22m
+_x001b_[2m      - waiting 500ms_x001b_[22m
+</v>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:D6"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:D9"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/result.xlsx
+++ b/result.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D9"/>
+  <dimension ref="A1:D18"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -527,9 +527,114 @@
 </v>
       </c>
     </row>
+    <row r="10">
+      <c r="A10" t="str">
+        <v>long4</v>
+      </c>
+      <c r="B10" t="str">
+        <v>ORDER</v>
+      </c>
+      <c r="C10" t="str">
+        <v>SUCCESS</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="str">
+        <v>truong1</v>
+      </c>
+      <c r="B11" t="str">
+        <v>LOGIN</v>
+      </c>
+      <c r="C11" t="str">
+        <v>SUCCESS</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="str">
+        <v>truong2</v>
+      </c>
+      <c r="B12" t="str">
+        <v>LOGIN</v>
+      </c>
+      <c r="C12" t="str">
+        <v>SUCCESS</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="str">
+        <v>truong</v>
+      </c>
+      <c r="B13" t="str">
+        <v>LOGIN</v>
+      </c>
+      <c r="C13" t="str">
+        <v>ERROR</v>
+      </c>
+      <c r="D13" t="str">
+        <v>Error: Login failed: truong</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="str">
+        <v>truong3</v>
+      </c>
+      <c r="B14" t="str">
+        <v>LOGIN</v>
+      </c>
+      <c r="C14" t="str">
+        <v>ERROR</v>
+      </c>
+      <c r="D14" t="str">
+        <v>Error: Login failed: truong3</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="str">
+        <v>truong1</v>
+      </c>
+      <c r="B15" t="str">
+        <v>ORDER</v>
+      </c>
+      <c r="C15" t="str">
+        <v>SUCCESS</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="str">
+        <v>truong2</v>
+      </c>
+      <c r="B16" t="str">
+        <v>ORDER</v>
+      </c>
+      <c r="C16" t="str">
+        <v>SUCCESS</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="str">
+        <v>truong</v>
+      </c>
+      <c r="B17" t="str">
+        <v>ORDER</v>
+      </c>
+      <c r="C17" t="str">
+        <v>SKIP_NO_LOGIN</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="str">
+        <v>truong3</v>
+      </c>
+      <c r="B18" t="str">
+        <v>ORDER</v>
+      </c>
+      <c r="C18" t="str">
+        <v>SKIP_NO_LOGIN</v>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:D9"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:D18"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/result.xlsx
+++ b/result.xlsx
@@ -1,41 +1,107 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29127"/>
   <workbookPr codeName="ThisWorkbook"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\NIC\Desktop\Test_2nd\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FE9B253F-0B58-4BDA-9A92-FE19D4A61997}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <bookViews>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+  </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
+  <calcPr calcId="0"/>
 </workbook>
 </file>
 
-<file path=xl/metadata.xml><?xml version="1.0" encoding="utf-8"?>
-<metadata xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xlrd="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata" xmlns:xda="http://schemas.microsoft.com/office/spreadsheetml/2017/dynamicarray">
-  <metadataTypes count="1">
-    <metadataType name="XLDAPR" minSupportedVersion="120000" copy="1" pasteAll="1" pasteValues="1" merge="1" splitFirst="1" rowColShift="1" clearFormats="1" clearComments="1" assign="1" coerce="1" cellMeta="1"/>
-  </metadataTypes>
-  <futureMetadata name="XLDAPR" count="1">
-    <bk>
-      <extLst>
-        <ext uri="{bdbb8cdc-fa1e-496e-a857-3c3f30c029c3}">
-          <xda:dynamicArrayProperties fDynamic="1" fCollapsed="0"/>
-        </ext>
-      </extLst>
-    </bk>
-  </futureMetadata>
-  <cellMetadata count="1">
-    <bk>
-      <rc t="1" v="0"/>
-    </bk>
-  </cellMetadata>
-</metadata>
+<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="50" uniqueCount="25">
+  <si>
+    <t>username</t>
+  </si>
+  <si>
+    <t>step</t>
+  </si>
+  <si>
+    <t>status</t>
+  </si>
+  <si>
+    <t>orderCode</t>
+  </si>
+  <si>
+    <t>result</t>
+  </si>
+  <si>
+    <t>fromStatus</t>
+  </si>
+  <si>
+    <t>toStatus</t>
+  </si>
+  <si>
+    <t>processed</t>
+  </si>
+  <si>
+    <t>truong1</t>
+  </si>
+  <si>
+    <t>ORDER_ADMIN</t>
+  </si>
+  <si>
+    <t>SKIP_NO_LOGIN</t>
+  </si>
+  <si>
+    <t>truong2</t>
+  </si>
+  <si>
+    <t>Hoàn thành</t>
+  </si>
+  <si>
+    <t>OD-260415-276122389089</t>
+  </si>
+  <si>
+    <t>ALREADY_AT_STEP</t>
+  </si>
+  <si>
+    <t>OD-260415-382365630824</t>
+  </si>
+  <si>
+    <t>OD-260415-450352838835</t>
+  </si>
+  <si>
+    <t>Đã hủy</t>
+  </si>
+  <si>
+    <t>OD-260415-914550502387</t>
+  </si>
+  <si>
+    <t>OD-260415-409944183770</t>
+  </si>
+  <si>
+    <t>CHANGED</t>
+  </si>
+  <si>
+    <t>Đã giao</t>
+  </si>
+  <si>
+    <t>SUCCESS</t>
+  </si>
+  <si>
+    <t>truong</t>
+  </si>
+  <si>
+    <t>truong3</t>
+  </si>
+</sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:vt="http://schemas.openxmlformats.org/officeDocument/2006/docPropsVTypes">
-  <numFmts count="1">
-    <numFmt numFmtId="56" formatCode="&quot;上午/下午 &quot;hh&quot;時&quot;mm&quot;分&quot;ss&quot;秒 &quot;"/>
-  </numFmts>
-  <fonts count="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <fonts count="1" x14ac:knownFonts="1">
     <font>
       <sz val="12"/>
       <color theme="1"/>
@@ -65,13 +131,21 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
   <cellXfs count="1">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleMedium4"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
@@ -396,245 +470,195 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D18"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <dimension ref="A1:H10"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="22.3984375" customWidth="1"/>
+    <col min="2" max="2" width="13.59765625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="14.19921875" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="22.8984375" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="16.59765625" bestFit="1" customWidth="1"/>
+    <col min="6" max="7" width="10.796875" bestFit="1" customWidth="1"/>
+  </cols>
   <sheetData>
-    <row r="1">
-      <c r="A1" t="str">
-        <v>username</v>
-      </c>
-      <c r="B1" t="str">
-        <v>step</v>
-      </c>
-      <c r="C1" t="str">
-        <v>status</v>
-      </c>
-      <c r="D1" t="str">
-        <v>error</v>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="str">
-        <v>long5</v>
-      </c>
-      <c r="B2" t="str">
-        <v>LOGIN</v>
-      </c>
-      <c r="C2" t="str">
-        <v>SUCCESS</v>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="str">
-        <v>long4</v>
-      </c>
-      <c r="B3" t="str">
-        <v>LOGIN</v>
-      </c>
-      <c r="C3" t="str">
-        <v>SUCCESS</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="str">
-        <v>long</v>
-      </c>
-      <c r="B4" t="str">
-        <v>LOGIN</v>
-      </c>
-      <c r="C4" t="str">
-        <v>ERROR</v>
-      </c>
-      <c r="D4" t="str">
-        <v>Error: Login failed: long</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="str">
-        <v>long3</v>
-      </c>
-      <c r="B5" t="str">
-        <v>LOGIN</v>
-      </c>
-      <c r="C5" t="str">
-        <v>SUCCESS</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="str">
-        <v>tuan</v>
-      </c>
-      <c r="B6" t="str">
-        <v>LOGIN</v>
-      </c>
-      <c r="C6" t="str">
-        <v>ERROR</v>
-      </c>
-      <c r="D6" t="str">
-        <v>Error: Login failed: tuan</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="str">
-        <v>long</v>
-      </c>
-      <c r="B7" t="str">
-        <v>ORDER</v>
-      </c>
-      <c r="C7" t="str">
-        <v>SKIP_NO_LOGIN</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="str">
-        <v>tuan</v>
-      </c>
-      <c r="B8" t="str">
-        <v>ORDER</v>
-      </c>
-      <c r="C8" t="str">
-        <v>SKIP_NO_LOGIN</v>
-      </c>
-    </row>
-    <row r="9" xml:space="preserve">
-      <c r="A9" t="str">
-        <v>long5</v>
-      </c>
-      <c r="B9" t="str">
-        <v>ORDER</v>
-      </c>
-      <c r="C9" t="str">
-        <v>ERROR</v>
-      </c>
-      <c r="D9" t="str" xml:space="preserve">
-        <v xml:space="preserve">Error: locator.click: Target page, context or browser has been closed
-Call log:
-_x001b_[2m  - waiting for getByText('Thêm vào giỏ hàng', { exact: true })_x001b_[22m
-_x001b_[2m    - locator resolved to &lt;span class="inline-flex items-center gap-2"&gt;Thêm vào giỏ hàng&lt;/span&gt;_x001b_[22m
-_x001b_[2m  - attempting click action_x001b_[22m
-_x001b_[2m    2 × waiting for element to be visible, enabled and stable_x001b_[22m
-_x001b_[2m      - element is not enabled_x001b_[22m
-_x001b_[2m    - retrying click action_x001b_[22m
-_x001b_[2m    - waiting 20ms_x001b_[22m
-_x001b_[2m    2 × waiting for element to be visible, enabled and stable_x001b_[22m
-_x001b_[2m      - element is not enabled_x001b_[22m
-_x001b_[2m    - retrying click action_x001b_[22m
-_x001b_[2m      - waiting 100ms_x001b_[22m
-_x001b_[2m    8 × waiting for element to be visible, enabled and stable_x001b_[22m
-_x001b_[2m      - element is not enabled_x001b_[22m
-_x001b_[2m    - retrying click action_x001b_[22m
-_x001b_[2m      - waiting 500ms_x001b_[22m
-</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="str">
-        <v>long4</v>
-      </c>
-      <c r="B10" t="str">
-        <v>ORDER</v>
-      </c>
-      <c r="C10" t="str">
-        <v>SUCCESS</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="str">
-        <v>truong1</v>
-      </c>
-      <c r="B11" t="str">
-        <v>LOGIN</v>
-      </c>
-      <c r="C11" t="str">
-        <v>SUCCESS</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="str">
-        <v>truong2</v>
-      </c>
-      <c r="B12" t="str">
-        <v>LOGIN</v>
-      </c>
-      <c r="C12" t="str">
-        <v>SUCCESS</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="str">
-        <v>truong</v>
-      </c>
-      <c r="B13" t="str">
-        <v>LOGIN</v>
-      </c>
-      <c r="C13" t="str">
-        <v>ERROR</v>
-      </c>
-      <c r="D13" t="str">
-        <v>Error: Login failed: truong</v>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="str">
-        <v>truong3</v>
-      </c>
-      <c r="B14" t="str">
-        <v>LOGIN</v>
-      </c>
-      <c r="C14" t="str">
-        <v>ERROR</v>
-      </c>
-      <c r="D14" t="str">
-        <v>Error: Login failed: truong3</v>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="str">
-        <v>truong1</v>
-      </c>
-      <c r="B15" t="str">
-        <v>ORDER</v>
-      </c>
-      <c r="C15" t="str">
-        <v>SUCCESS</v>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="str">
-        <v>truong2</v>
-      </c>
-      <c r="B16" t="str">
-        <v>ORDER</v>
-      </c>
-      <c r="C16" t="str">
-        <v>SUCCESS</v>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="str">
-        <v>truong</v>
-      </c>
-      <c r="B17" t="str">
-        <v>ORDER</v>
-      </c>
-      <c r="C17" t="str">
-        <v>SKIP_NO_LOGIN</v>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="str">
-        <v>truong3</v>
-      </c>
-      <c r="B18" t="str">
-        <v>ORDER</v>
-      </c>
-      <c r="C18" t="str">
-        <v>SKIP_NO_LOGIN</v>
+    <row r="1" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" t="s">
+        <v>6</v>
+      </c>
+      <c r="H1" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="2" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A2" t="s">
+        <v>8</v>
+      </c>
+      <c r="B2" t="s">
+        <v>9</v>
+      </c>
+      <c r="C2" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="3" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A3" t="s">
+        <v>11</v>
+      </c>
+      <c r="B3" t="s">
+        <v>12</v>
+      </c>
+      <c r="D3" t="s">
+        <v>13</v>
+      </c>
+      <c r="E3" t="s">
+        <v>14</v>
+      </c>
+      <c r="F3" t="s">
+        <v>12</v>
+      </c>
+      <c r="G3" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="4" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A4" t="s">
+        <v>11</v>
+      </c>
+      <c r="B4" t="s">
+        <v>12</v>
+      </c>
+      <c r="D4" t="s">
+        <v>15</v>
+      </c>
+      <c r="E4" t="s">
+        <v>14</v>
+      </c>
+      <c r="F4" t="s">
+        <v>12</v>
+      </c>
+      <c r="G4" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="5" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A5" t="s">
+        <v>11</v>
+      </c>
+      <c r="B5" t="s">
+        <v>12</v>
+      </c>
+      <c r="D5" t="s">
+        <v>16</v>
+      </c>
+      <c r="E5" t="s">
+        <v>14</v>
+      </c>
+      <c r="F5" t="s">
+        <v>12</v>
+      </c>
+      <c r="G5" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="6" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A6" t="s">
+        <v>11</v>
+      </c>
+      <c r="B6" t="s">
+        <v>17</v>
+      </c>
+      <c r="D6" t="s">
+        <v>18</v>
+      </c>
+      <c r="E6" t="s">
+        <v>14</v>
+      </c>
+      <c r="F6" t="s">
+        <v>17</v>
+      </c>
+      <c r="G6" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="7" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A7" t="s">
+        <v>11</v>
+      </c>
+      <c r="B7" t="s">
+        <v>12</v>
+      </c>
+      <c r="D7" t="s">
+        <v>19</v>
+      </c>
+      <c r="E7" t="s">
+        <v>20</v>
+      </c>
+      <c r="F7" t="s">
+        <v>21</v>
+      </c>
+      <c r="G7" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="8" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A8" t="s">
+        <v>11</v>
+      </c>
+      <c r="B8" t="s">
+        <v>9</v>
+      </c>
+      <c r="C8" t="s">
+        <v>22</v>
+      </c>
+      <c r="H8">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="9" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A9" t="s">
+        <v>23</v>
+      </c>
+      <c r="B9" t="s">
+        <v>9</v>
+      </c>
+      <c r="C9" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="10" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A10" t="s">
+        <v>24</v>
+      </c>
+      <c r="B10" t="s">
+        <v>9</v>
+      </c>
+      <c r="C10" t="s">
+        <v>10</v>
       </c>
     </row>
   </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:D18"/>
+    <ignoredError sqref="A1:H10" numberStoredAsText="1"/>
   </ignoredErrors>
 </worksheet>
 </file>